--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T08:22:13+00:00</t>
+    <t>2026-01-09T09:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T09:20:56+00:00</t>
+    <t>2026-01-09T10:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T10:00:38+00:00</t>
+    <t>2026-01-09T10:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T10:25:42+00:00</t>
+    <t>2026-01-12T10:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:02:02+00:00</t>
+    <t>2026-01-13T16:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T16:51:50+00:00</t>
+    <t>2026-01-15T13:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T13:52:15+00:00</t>
+    <t>2026-01-22T17:48:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
+++ b/409-sfe---projet-personnalisé---contactpersonnephysique/ig/StructureDefinition-tddui-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T17:48:29+00:00</t>
+    <t>2026-01-26T10:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
